--- a/survey_templates/031_youth_employment_survey--survey_templates.xlsx
+++ b/survey_templates/031_youth_employment_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1213,12 +1213,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_31,_'label':_'working'}</t>
+          <t>working</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 31, 'label': 'Working'}</t>
+          <t>Working</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_32,_'label':_'not_working'}</t>
+          <t>not_working</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 32, 'label': 'Not working'}</t>
+          <t>Not working</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_33,_'label':_'in_school'}</t>
+          <t>in_school</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 33, 'label': 'In school'}</t>
+          <t>In school</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_41,_'label':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 41, 'label': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1314,29 +1314,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_42,_'label':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 42, 'label': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_type_choices</t>
+          <t>job_type_list_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_42,_'label':_'part-time'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 42, 'label': 'Part-time'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_71,_'label':_'sales'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 71, 'label': 'Sales'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1365,29 +1365,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_72,_'label':_'marketing'}</t>
+          <t>engineering</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 72, 'label': 'Marketing'}</t>
+          <t>Engineering</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_type_list_choices</t>
+          <t>hours_worked_last_week_list_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_73,_'label':_'engineering'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 73, 'label': 'Engineering'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_81,_'label':_'monday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 81, 'label': 'Monday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1416,29 +1416,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_82,_'label':_'tuesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 82, 'label': 'Tuesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hours_worked_last_week_list_choices</t>
+          <t>months_worked_last_year_list_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_83,_'label':_'wednesday'}</t>
+          <t>january</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 83, 'label': 'Wednesday'}</t>
+          <t>January</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_101,_'label':_'january'}</t>
+          <t>february</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 101, 'label': 'January'}</t>
+          <t>February</t>
         </is>
       </c>
     </row>
@@ -1467,29 +1467,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_102,_'label':_'february'}</t>
+          <t>march</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 102, 'label': 'February'}</t>
+          <t>March</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>months_worked_last_year_list_choices</t>
+          <t>weeks_worked_this_year_list_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_103,_'label':_'march'}</t>
+          <t>week_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 103, 'label': 'March'}</t>
+          <t>Week 1</t>
         </is>
       </c>
     </row>
@@ -1501,29 +1501,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_121,_'label':_'week_1'}</t>
+          <t>week_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 121, 'label': 'Week 1'}</t>
+          <t>Week 2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>weeks_worked_this_year_list_choices</t>
+          <t>work_status_employer_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_122,_'label':_'week_2'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 122, 'label': 'Week 2'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_131,_'label':_'employed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 131, 'label': 'Employed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -1552,29 +1552,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_132,_'label':_'unemployed'}</t>
+          <t>self-employed</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 132, 'label': 'Unemployed'}</t>
+          <t>Self-employed</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>work_status_employer_choices</t>
+          <t>work_status_student_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_133,_'label':_'self-employed'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 133, 'label': 'Self-employed'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -1586,29 +1586,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_141,_'label':_'student'}</t>
+          <t>not_a_student</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 141, 'label': 'Student'}</t>
+          <t>Not a student</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>work_status_student_choices</t>
+          <t>education_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_142,_'label':_'not_a_student'}</t>
+          <t>high_school_graduate</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 142, 'label': 'Not a student'}</t>
+          <t>High school graduate</t>
         </is>
       </c>
     </row>
@@ -1620,12 +1620,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_151,_'label':_'high_school_graduate'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 151, 'label': 'High school graduate'}</t>
+          <t>Some college</t>
         </is>
       </c>
     </row>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_152,_'label':_'some_college'}</t>
+          <t>bachelor’s</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 152, 'label': 'Some college'}</t>
+          <t>Bachelor’s</t>
         </is>
       </c>
     </row>
@@ -1654,12 +1654,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_153,_'label':_'bachelor’s'}</t>
+          <t>post_graduate</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 153, 'label': 'Bachelor’s'}</t>
+          <t>Post graduate</t>
         </is>
       </c>
     </row>
@@ -1671,29 +1671,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_154,_'label':_'post_graduate'}</t>
+          <t>no_formal_education</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 154, 'label': 'Post graduate'}</t>
+          <t>No formal education</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>education_choices</t>
+          <t>skills_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_155,_'label':_'no_formal_education'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 155, 'label': 'No formal education'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -1705,12 +1705,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_161,_'label':_'communication'}</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 161, 'label': 'Communication'}</t>
+          <t>Teamwork</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_162,_'label':_'teamwork'}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 162, 'label': 'Teamwork'}</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -1739,12 +1739,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_163,_'label':_'leadership'}</t>
+          <t>problem-solving</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 163, 'label': 'Leadership'}</t>
+          <t>Problem-solving</t>
         </is>
       </c>
     </row>
@@ -1756,29 +1756,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_164,_'label':_'problem-solving'}</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 164, 'label': 'Problem-solving'}</t>
+          <t>Adaptability</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>skills_choices</t>
+          <t>work_experience_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_165,_'label':_'adaptability'}</t>
+          <t>0-1_year</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 165, 'label': 'Adaptability'}</t>
+          <t>0-1 year</t>
         </is>
       </c>
     </row>
@@ -1790,12 +1790,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_171,_'label':_'0-1_year'}</t>
+          <t>1-2_years</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 171, 'label': '0-1 year'}</t>
+          <t>1-2 years</t>
         </is>
       </c>
     </row>
@@ -1807,46 +1807,46 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_172,_'label':_'1-2_years'}</t>
+          <t>2-3_years</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 172, 'label': '1-2 years'}</t>
+          <t>2-3 years</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>work_experience_choices</t>
+          <t>job_satisfaction_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_172,_'label':_'1-2_years'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 172, 'label': '1-2 years'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>work_experience_choices</t>
+          <t>job_satisfaction_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_173,_'label':_'2-3_years'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 173, 'label': '2-3 years'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1858,46 +1858,46 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_181,_'label':_'neutral'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 181, 'label': 'Neutral'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>job_satisfaction_list_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_182,_'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 182, 'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>job_satisfaction_list_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_183,_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 183, 'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1909,46 +1909,46 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_191,_'label':_'satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 191, 'label': 'Satisfied'}</t>
+          <t>Not satisfied</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>job_satisfaction_list_choices</t>
+          <t>education_list_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_192,_'label':_'very_satisfied'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 192, 'label': 'Very satisfied'}</t>
+          <t>High school</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>job_satisfaction_list_choices</t>
+          <t>education_list_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_193,_'label':_'not_satisfied'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 193, 'label': 'Not satisfied'}</t>
+          <t>Some college</t>
         </is>
       </c>
     </row>
@@ -1960,12 +1960,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_261,_'label':_'high_school'}</t>
+          <t>bachelor’s_degree</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 261, 'label': 'High school'}</t>
+          <t>Bachelor’s degree</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_262,_'label':_'some_college'}</t>
+          <t>post_graduate</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 262, 'label': 'Some college'}</t>
+          <t>Post graduate</t>
         </is>
       </c>
     </row>
@@ -1994,46 +1994,46 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_263,_'label':_'bachelor’s_degree'}</t>
+          <t>no_formal_education</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 263, 'label': 'Bachelor’s degree'}</t>
+          <t>No formal education</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>education_list_choices</t>
+          <t>skills_list_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_264,_'label':_'post_graduate'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 264, 'label': 'Post graduate'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>education_list_choices</t>
+          <t>skills_list_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_265,_'label':_'no_formal_education'}</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 265, 'label': 'No formal education'}</t>
+          <t>Teamwork</t>
         </is>
       </c>
     </row>
@@ -2045,12 +2045,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_271,_'label':_'communication'}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 271, 'label': 'Communication'}</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_272,_'label':_'teamwork'}</t>
+          <t>problem-solving</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 272, 'label': 'Teamwork'}</t>
+          <t>Problem-solving</t>
         </is>
       </c>
     </row>
@@ -2079,46 +2079,46 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_273,_'label':_'leadership'}</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 273, 'label': 'Leadership'}</t>
+          <t>Adaptability</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>skills_list_choices</t>
+          <t>employment_status_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_274,_'label':_'problem-solving'}</t>
+          <t>working</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 274, 'label': 'Problem-solving'}</t>
+          <t>Working</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>skills_list_choices</t>
+          <t>employment_status_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'id':_275,_'label':_'adaptability'}</t>
+          <t>not_working</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'id': 275, 'label': 'Adaptability'}</t>
+          <t>Not working</t>
         </is>
       </c>
     </row>
@@ -2130,46 +2130,46 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'id':_291,_'label':_'working'}</t>
+          <t>in_school</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'id': 291, 'label': 'Working'}</t>
+          <t>In school</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>employment_status_choices</t>
+          <t>work_status_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'id':_292,_'label':_'not_working'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'id': 292, 'label': 'Not working'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>employment_status_choices</t>
+          <t>work_status_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'id':_293,_'label':_'in_school'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'id': 293, 'label': 'In school'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -2181,46 +2181,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'id':_301,_'label':_'employed'}</t>
+          <t>self-employed</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'id': 301, 'label': 'Employed'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>work_status_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>{'id':_302,_'label':_'unemployed'}</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>{'id': 302, 'label': 'Unemployed'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>work_status_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>{'id':_303,_'label':_'self-employed'}</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>{'id': 303, 'label': 'Self-employed'}</t>
+          <t>Self-employed</t>
         </is>
       </c>
     </row>
